--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\Issue list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\Issue-List-Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD80B160-F83D-4169-AF7A-8166533B70D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00362CD-D8E7-4D91-B794-20F6D3362920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>BU4</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>MERRY &amp; LUXSHARE (VIET NAM) CO.,LTD]</t>
+  </si>
+  <si>
+    <t>Luxvisions Innovation Technology (Yian) Co., Ltd.]</t>
+  </si>
+  <si>
+    <t>VISION</t>
   </si>
 </sst>
 </file>
@@ -413,7 +419,9 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -436,6 +444,9 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="O2" s="2"/>
     </row>
   </sheetData>

--- a/FILTER.xlsx
+++ b/FILTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARE\GIT HUB\Issue-List-Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00362CD-D8E7-4D91-B794-20F6D3362920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5257153D-57B5-4CAA-A2CB-BA991DE056C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>BU4</t>
   </si>
@@ -60,6 +60,21 @@
   </si>
   <si>
     <t>VISION</t>
+  </si>
+  <si>
+    <t>LDT</t>
+  </si>
+  <si>
+    <t>MICRON</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>GOERTEK MICROELECTRONICS VINA CO., LTD.]</t>
+  </si>
+  <si>
+    <t>LEADER TECH VIETNAM COMPANY LIMITED]</t>
   </si>
 </sst>
 </file>
@@ -422,9 +437,15 @@
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -447,9 +468,19 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="O2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>